--- a/34th_Backgammon-championships_2a_output.xlsx
+++ b/34th_Backgammon-championships_2a_output.xlsx
@@ -1156,7 +1156,7 @@
         <v>8</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">

--- a/34th_Backgammon-championships_2a_output.xlsx
+++ b/34th_Backgammon-championships_2a_output.xlsx
@@ -663,11 +663,6 @@
           <t>5171876</t>
         </is>
       </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>5171679</t>
-        </is>
-      </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
           <t>5171845</t>
@@ -869,11 +864,6 @@
       <c r="F9" s="1" t="inlineStr">
         <is>
           <t>5171192</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>5171195</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
@@ -1025,63 +1015,61 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1248,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>6</v>
@@ -1311,12 +1299,6 @@
       <c r="M7" t="n">
         <v>8</v>
       </c>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>11</v>
-      </c>
       <c r="P7" t="n">
         <v>11</v>
       </c>
@@ -1388,7 +1370,7 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
         <v>5</v>
@@ -1492,7 +1474,7 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>9</v>
@@ -1553,12 +1535,6 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>11</v>
-      </c>
-      <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
